--- a/SAEN PEÑA/Septiembre/SAENZ_EXPENSAS-Septiembre.xlsx
+++ b/SAEN PEÑA/Septiembre/SAENZ_EXPENSAS-Septiembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\SAEN PEÑA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\SAEN PEÑA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6AC89B-3567-4202-BE0D-B48155BE4839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCD4499-420B-4E86-A694-D3A7E291CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="prorrateo  (2)" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -233,15 +233,6 @@
   </si>
   <si>
     <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Salvatierra Nicolas - Trabajos realizados para intentar desobstruir camara septica - No se consigue, se encuentra pozo lleno y se sugiere desagotar</t>
-  </si>
-  <si>
-    <t>Materiales para la obra</t>
-  </si>
-  <si>
-    <t>Ingreso por pago de materiales de obra</t>
   </si>
   <si>
     <t>PRESUPUESTO APROBADO - MANO DE OBRA GAS Y CLOACAS</t>
@@ -1068,7 +1059,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1144,7 +1135,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1281,14 +1271,9 @@
     <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="15" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1714,63 +1699,63 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="100" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="28"/>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
       <c r="E7" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="102"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="F7" s="101"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1778,16 +1763,16 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="105" t="s">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="104" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="101"/>
+      <c r="B11" s="100"/>
       <c r="C11" s="12"/>
       <c r="D11" s="5"/>
       <c r="E11" s="126" t="s">
@@ -1795,26 +1780,26 @@
       </c>
       <c r="F11" s="126"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
-      <c r="B12" s="103"/>
-      <c r="C12" s="111"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="110"/>
       <c r="D12" s="5"/>
       <c r="E12" s="48" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="49">
-        <v>135981.60904773313</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
+        <v>890833.31141901179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="111">
+      <c r="C13" s="109">
         <v>35601</v>
       </c>
       <c r="D13" s="36"/>
@@ -1823,17 +1808,17 @@
       </c>
       <c r="F13" s="51">
         <f>'prorrateo '!F11</f>
-        <v>781188.82237127877</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="103" t="s">
+        <v>646382.94151380809</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="103" t="s">
+      <c r="B14" s="102" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="111">
+      <c r="C14" s="109">
         <v>27930.06</v>
       </c>
       <c r="D14" s="5"/>
@@ -1841,301 +1826,277 @@
         <v>22</v>
       </c>
       <c r="F14" s="51">
-        <f>-(C36)</f>
-        <v>-253869.76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="101" t="s">
+        <f>-(C35)</f>
+        <v>-181966.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="73">
         <v>32800</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="51">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="101"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="74"/>
-      <c r="E16" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="51">
-        <v>-993980.26</v>
-      </c>
+      <c r="E15" s="50"/>
+      <c r="F15" s="51"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="100"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="73"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="51"/>
       <c r="G16" s="16"/>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="106"/>
-      <c r="B17" s="107"/>
-      <c r="C17" s="81">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="105"/>
+      <c r="B17" s="106"/>
+      <c r="C17" s="80">
         <f>SUM(C12:C16)</f>
         <v>96331.06</v>
       </c>
       <c r="E17" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="125">
         <f>SUM(F12:F16)</f>
-        <v>869320.41141901189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="105" t="s">
+        <v>1355249.5529328201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="104" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="101"/>
-      <c r="C18" s="108"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="5"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
     </row>
-    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="101" t="s">
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="109" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="74">
-        <f xml:space="preserve"> 53894+53894*5%</f>
-        <v>56588.7</v>
+      <c r="B19" s="108" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="73">
+        <f xml:space="preserve"> 56588+56588*3%</f>
+        <v>58285.64</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
     </row>
-    <row r="20" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="127" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="128"/>
-      <c r="C20" s="74">
-        <v>73600</v>
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="100" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="108"/>
+      <c r="C20" s="109">
+        <v>27350</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
     </row>
-    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="101" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="109"/>
-      <c r="C21" s="111">
-        <v>27350</v>
-      </c>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="108"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="5"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="101" t="s">
-        <v>67</v>
-      </c>
-      <c r="B22" s="109"/>
-      <c r="C22" s="110">
-        <f>555359-232356.86</f>
-        <v>323002.14</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="105"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="123">
+        <f>SUM(C18:C21)</f>
+        <v>85635.64</v>
       </c>
       <c r="D22" s="5"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="106"/>
-      <c r="B23" s="107"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="41"/>
       <c r="C23" s="124">
-        <f>SUM(C18:C22)</f>
-        <v>480540.84</v>
+        <f>+C22+C17</f>
+        <v>181966.7</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="125">
-        <f>+C23+C17</f>
-        <v>576871.9</v>
-      </c>
-      <c r="D24" s="5"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="62" t="s">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="76"/>
-      <c r="C25" s="77"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="46"/>
+    </row>
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="46"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="44"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="45">
+        <v>0</v>
+      </c>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44"/>
-      <c r="B28" s="43"/>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="53"/>
+      <c r="B28" s="54"/>
       <c r="C28" s="45">
         <v>0</v>
       </c>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="54"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="45">
-        <v>0</v>
-      </c>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="71"/>
+      <c r="B29" s="72"/>
+      <c r="C29" s="74"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="72"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="75"/>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="71"/>
+      <c r="B30" s="78"/>
+      <c r="C30" s="79"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="72"/>
-      <c r="B31" s="79"/>
-      <c r="C31" s="80"/>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="71"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="74">
+        <v>0</v>
+      </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="72"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="75">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="56" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="57"/>
-      <c r="C33" s="58">
-        <f>SUM(C28:C32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="B32" s="56"/>
+      <c r="C32" s="57">
+        <f>SUM(C27:C31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="45">
-        <f>C24-C22</f>
-        <v>253869.76</v>
-      </c>
+      <c r="C33" s="45">
+        <f>C23-C21</f>
+        <v>181966.7</v>
+      </c>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="70">
+        <f>+C23</f>
+        <v>181966.7</v>
+      </c>
+      <c r="E34" s="103"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="71">
-        <f>+C24</f>
-        <v>576871.9</v>
-      </c>
-      <c r="E35" s="104"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="56" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="58">
-        <f>C34</f>
-        <v>253869.76</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B35" s="56"/>
+      <c r="C35" s="57">
+        <f>C33</f>
+        <v>181966.7</v>
+      </c>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D42" s="16"/>
       <c r="E42" s="16"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="16"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D45" s="16"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="19"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="19"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="20"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="18"/>
       <c r="B57" s="18"/>
-      <c r="C57" s="20"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="18"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="18"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="18"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="18"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A20:B20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2153,29 +2114,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
       <c r="D1" s="26"/>
       <c r="E1" s="25" t="s">
         <v>41</v>
@@ -2187,31 +2148,31 @@
       <c r="H1" s="26"/>
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
-      <c r="K1" s="64">
-        <v>555359.13500000001</v>
+      <c r="K1" s="63">
+        <v>181966.7</v>
       </c>
       <c r="L1" s="27"/>
     </row>
-    <row r="2" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="65" t="str">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="64" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de SEPTIEMBRE</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="68" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="70"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="69"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2249,7 +2210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2275,11 +2236,11 @@
       <c r="K4" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="L4" s="59" t="s">
+      <c r="L4" s="58" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2293,23 +2254,26 @@
         <v>0.1512</v>
       </c>
       <c r="E5" s="34">
-        <v>83970.301212000006</v>
-      </c>
-      <c r="F5" s="74"/>
-      <c r="G5" s="60">
+        <v>174994.10772580802</v>
+      </c>
+      <c r="F5" s="73">
+        <f>E5</f>
+        <v>174994.10772580802</v>
+      </c>
+      <c r="G5" s="59">
         <f>E5-F5</f>
-        <v>83970.301212000006</v>
-      </c>
-      <c r="H5" s="63">
+        <v>0</v>
+      </c>
+      <c r="H5" s="62">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>7053.5053018080007</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="31">
         <f>K1*D5</f>
-        <v>83970.301212000006</v>
+        <v>27513.365040000001</v>
       </c>
       <c r="K5" s="15">
         <f>K2*D5</f>
@@ -2317,10 +2281,10 @@
       </c>
       <c r="L5" s="32">
         <f>J5+K5+H5+G5</f>
-        <v>174994.10772580802</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>27513.365040000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2334,17 +2298,17 @@
         <v>0.15690000000000001</v>
       </c>
       <c r="E6" s="34">
-        <v>154602.20380062901</v>
-      </c>
-      <c r="F6" s="74">
+        <v>87135.848281500002</v>
+      </c>
+      <c r="F6" s="73">
         <f t="shared" ref="F6:F10" si="0">E6</f>
-        <v>154602.20380062901</v>
-      </c>
-      <c r="G6" s="60">
+        <v>87135.848281500002</v>
+      </c>
+      <c r="G6" s="59">
         <f t="shared" ref="G6:G8" si="1">E6-F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="63">
+      <c r="H6" s="62">
         <f t="shared" ref="H6:H10" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
         <v>0</v>
       </c>
@@ -2353,7 +2317,7 @@
       </c>
       <c r="J6" s="31">
         <f>K1*D6</f>
-        <v>87135.848281500002</v>
+        <v>28550.575230000002</v>
       </c>
       <c r="K6" s="15">
         <f>K2*D6</f>
@@ -2361,10 +2325,10 @@
       </c>
       <c r="L6" s="32">
         <f>J6+K6+H6+G6</f>
-        <v>87135.848281500002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28550.575230000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2378,17 +2342,17 @@
         <v>0.15820000000000001</v>
       </c>
       <c r="E7" s="34">
-        <v>190608.52024670265</v>
-      </c>
-      <c r="F7" s="74">
+        <v>87857.815157000005</v>
+      </c>
+      <c r="F7" s="73">
         <f t="shared" si="0"/>
-        <v>190608.52024670265</v>
-      </c>
-      <c r="G7" s="60">
+        <v>87857.815157000005</v>
+      </c>
+      <c r="G7" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="63">
+      <c r="H7" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2397,7 +2361,7 @@
       </c>
       <c r="J7" s="31">
         <f>K1*D7</f>
-        <v>87857.815157000005</v>
+        <v>28787.131940000003</v>
       </c>
       <c r="K7" s="15">
         <f>K2*D7</f>
@@ -2405,10 +2369,10 @@
       </c>
       <c r="L7" s="32">
         <f t="shared" ref="L7:L9" si="3">J7+K7+H7+G7</f>
-        <v>87857.815157000005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28787.131940000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2422,17 +2386,17 @@
         <v>0.19800000000000001</v>
       </c>
       <c r="E8" s="34">
-        <v>238561.86478411587</v>
-      </c>
-      <c r="F8" s="74">
+        <v>109961.10873000001</v>
+      </c>
+      <c r="F8" s="73">
         <f t="shared" si="0"/>
-        <v>238561.86478411587</v>
-      </c>
-      <c r="G8" s="60">
+        <v>109961.10873000001</v>
+      </c>
+      <c r="G8" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="63">
+      <c r="H8" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2441,7 +2405,7 @@
       </c>
       <c r="J8" s="31">
         <f>K1*D8</f>
-        <v>109961.10873000001</v>
+        <v>36029.406600000002</v>
       </c>
       <c r="K8" s="15">
         <f>K2*D8</f>
@@ -2449,10 +2413,10 @@
       </c>
       <c r="L8" s="32">
         <f t="shared" si="3"/>
-        <v>109961.10873000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>36029.406600000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2468,15 +2432,15 @@
       <c r="E9" s="34">
         <v>88413.174292000011</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F9" s="73">
         <f t="shared" si="0"/>
         <v>88413.174292000011</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="59">
         <f>E9-F9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2485,7 +2449,7 @@
       </c>
       <c r="J9" s="31">
         <f>K1*D9</f>
-        <v>88413.174292000011</v>
+        <v>28969.098640000004</v>
       </c>
       <c r="K9" s="15">
         <f>K2*D9</f>
@@ -2493,10 +2457,10 @@
       </c>
       <c r="L9" s="32">
         <f t="shared" si="3"/>
-        <v>88413.174292000011</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>28969.098640000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>6</v>
       </c>
@@ -2510,17 +2474,17 @@
         <v>0.17649999999999999</v>
       </c>
       <c r="E10" s="34">
-        <v>109003.0592478312</v>
-      </c>
-      <c r="F10" s="74">
+        <v>98020.887327499993</v>
+      </c>
+      <c r="F10" s="73">
         <f t="shared" si="0"/>
-        <v>109003.0592478312</v>
-      </c>
-      <c r="G10" s="60">
+        <v>98020.887327499993</v>
+      </c>
+      <c r="G10" s="59">
         <f>E10-F10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="63">
+      <c r="H10" s="62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -2529,7 +2493,7 @@
       </c>
       <c r="J10" s="31">
         <f>K1*D10</f>
-        <v>98020.887327499993</v>
+        <v>32117.12255</v>
       </c>
       <c r="K10" s="15">
         <f>K2*D10</f>
@@ -2537,10 +2501,10 @@
       </c>
       <c r="L10" s="32">
         <f>J10+K10+H10+G10</f>
-        <v>98020.887327499993</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>32117.12255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -2552,19 +2516,19 @@
       </c>
       <c r="E11" s="35">
         <f t="shared" ref="E11" si="4">SUM(E5:E10)</f>
-        <v>865159.12358327874</v>
+        <v>646382.94151380809</v>
       </c>
       <c r="F11" s="35">
         <f>SUM(F5:F10)</f>
-        <v>781188.82237127877</v>
+        <v>646382.94151380809</v>
       </c>
       <c r="G11" s="42">
         <f>SUM(G5:G10)</f>
-        <v>83970.301212000006</v>
+        <v>0</v>
       </c>
       <c r="H11" s="42">
         <f t="shared" ref="H11:K11" si="5">SUM(H5:H10)</f>
-        <v>7053.5053018080007</v>
+        <v>0</v>
       </c>
       <c r="I11" s="11">
         <f t="shared" si="5"/>
@@ -2572,7 +2536,7 @@
       </c>
       <c r="J11" s="39">
         <f t="shared" si="5"/>
-        <v>555359.13500000001</v>
+        <v>181966.7</v>
       </c>
       <c r="K11" s="39">
         <f t="shared" si="5"/>
@@ -2580,27 +2544,27 @@
       </c>
       <c r="L11" s="42">
         <f>SUM(L5:L10)</f>
-        <v>646382.94151380809</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="129"/>
-      <c r="B12" s="129"/>
-      <c r="C12" s="129"/>
-      <c r="D12" s="129"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="129"/>
-      <c r="G12" s="129"/>
-      <c r="H12" s="129"/>
-      <c r="I12" s="129"/>
-      <c r="J12" s="129"/>
-      <c r="K12" s="129"/>
-      <c r="L12" s="129"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>181966.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="127"/>
+      <c r="B12" s="127"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="127"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="127"/>
+      <c r="L12" s="127"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="L13" s="6"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
     </row>
@@ -2617,232 +2581,232 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="135" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-    </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="138" t="s">
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="136" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="139"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="141">
+      <c r="B2" s="137"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="139">
         <v>565</v>
       </c>
-      <c r="E2" s="142"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-    </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="143" t="s">
+      <c r="E2" s="140"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="145" t="s">
+      <c r="D3" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="130" t="s">
+      <c r="E3" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="130" t="s">
+      <c r="F3" s="128" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="130" t="s">
+      <c r="G3" s="128" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="144"/>
-      <c r="B4" s="144"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="84">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="142"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="83">
         <v>1</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="84">
         <v>0.1512</v>
       </c>
-      <c r="E5" s="88">
+      <c r="E5" s="87">
         <v>85</v>
       </c>
-      <c r="F5" s="88">
-        <v>0</v>
-      </c>
-      <c r="G5" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="84">
+      <c r="F5" s="87">
+        <v>0</v>
+      </c>
+      <c r="G5" s="87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="83">
         <v>2</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="85" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="84">
         <v>0.15690000000000001</v>
       </c>
-      <c r="E6" s="88">
+      <c r="E6" s="87">
         <v>89</v>
       </c>
-      <c r="F6" s="88">
-        <v>0</v>
-      </c>
-      <c r="G6" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="84">
+      <c r="F6" s="87">
+        <v>0</v>
+      </c>
+      <c r="G6" s="87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="83">
         <v>3</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="84">
         <v>0.15820000000000001</v>
       </c>
-      <c r="E7" s="88">
+      <c r="E7" s="87">
         <v>89</v>
       </c>
-      <c r="F7" s="88">
-        <v>0</v>
-      </c>
-      <c r="G7" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="84">
+      <c r="F7" s="87">
+        <v>0</v>
+      </c>
+      <c r="G7" s="87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="83">
         <v>4</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="98" t="s">
+      <c r="C8" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="84">
         <v>0.19800000000000001</v>
       </c>
-      <c r="E8" s="88">
+      <c r="E8" s="87">
         <v>112</v>
       </c>
-      <c r="F8" s="88">
-        <v>0</v>
-      </c>
-      <c r="G8" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="84">
+      <c r="F8" s="87">
+        <v>0</v>
+      </c>
+      <c r="G8" s="87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="83">
         <v>5</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="87" t="s">
+      <c r="C9" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="84">
         <v>0.15920000000000001</v>
       </c>
-      <c r="E9" s="88">
+      <c r="E9" s="87">
         <v>90</v>
       </c>
-      <c r="F9" s="88">
-        <v>0</v>
-      </c>
-      <c r="G9" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="89">
+      <c r="F9" s="87">
+        <v>0</v>
+      </c>
+      <c r="G9" s="87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="88">
         <v>6</v>
       </c>
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="90" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="92" t="s">
+      <c r="C10" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="90">
+      <c r="D10" s="89">
         <v>0.17649999999999999</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="92">
         <v>100</v>
       </c>
-      <c r="F10" s="93">
-        <v>0</v>
-      </c>
-      <c r="G10" s="93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="94" t="s">
+      <c r="F10" s="92">
+        <v>0</v>
+      </c>
+      <c r="G10" s="92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="95"/>
-      <c r="D11" s="96">
+      <c r="B11" s="94"/>
+      <c r="C11" s="94"/>
+      <c r="D11" s="95">
         <v>1</v>
       </c>
-      <c r="E11" s="96">
+      <c r="E11" s="95">
         <v>565</v>
       </c>
-      <c r="F11" s="96" t="s">
+      <c r="F11" s="95" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="97" t="s">
+      <c r="G11" s="96" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="130"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2869,36 +2833,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="112" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="147">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="145">
         <v>4500000</v>
       </c>
-      <c r="H1" s="147"/>
-      <c r="I1" s="116"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H1" s="145"/>
+      <c r="I1" s="115"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
@@ -2927,7 +2891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2948,7 +2912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>1</v>
       </c>
@@ -2958,16 +2922,16 @@
       <c r="C4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="117">
+      <c r="D4" s="116">
         <v>0.1512</v>
       </c>
       <c r="E4" s="34">
         <v>0</v>
       </c>
-      <c r="F4" s="74">
-        <v>0</v>
-      </c>
-      <c r="G4" s="118">
+      <c r="F4" s="73">
+        <v>0</v>
+      </c>
+      <c r="G4" s="117">
         <f>E4-F4</f>
         <v>0</v>
       </c>
@@ -2980,7 +2944,7 @@
         <v>680400</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>2</v>
       </c>
@@ -2990,16 +2954,16 @@
       <c r="C5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="117">
+      <c r="D5" s="116">
         <v>0.15690000000000001</v>
       </c>
       <c r="E5" s="34">
         <v>0</v>
       </c>
-      <c r="F5" s="74">
-        <v>0</v>
-      </c>
-      <c r="G5" s="118">
+      <c r="F5" s="73">
+        <v>0</v>
+      </c>
+      <c r="G5" s="117">
         <f t="shared" ref="G5:G7" si="1">E5-F5</f>
         <v>0</v>
       </c>
@@ -3012,7 +2976,7 @@
         <v>706050</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>3</v>
       </c>
@@ -3022,16 +2986,16 @@
       <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="117">
+      <c r="D6" s="116">
         <v>0.15820000000000001</v>
       </c>
       <c r="E6" s="34">
         <v>0</v>
       </c>
-      <c r="F6" s="74">
-        <v>0</v>
-      </c>
-      <c r="G6" s="118">
+      <c r="F6" s="73">
+        <v>0</v>
+      </c>
+      <c r="G6" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3044,7 +3008,7 @@
         <v>711900</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>4</v>
       </c>
@@ -3054,16 +3018,16 @@
       <c r="C7" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="117">
+      <c r="D7" s="116">
         <v>0.19800000000000001</v>
       </c>
       <c r="E7" s="34">
         <v>0</v>
       </c>
-      <c r="F7" s="74">
-        <v>0</v>
-      </c>
-      <c r="G7" s="118">
+      <c r="F7" s="73">
+        <v>0</v>
+      </c>
+      <c r="G7" s="117">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3076,7 +3040,7 @@
         <v>891000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>5</v>
       </c>
@@ -3086,16 +3050,16 @@
       <c r="C8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="117">
+      <c r="D8" s="116">
         <v>0.15920000000000001</v>
       </c>
       <c r="E8" s="34">
         <v>0</v>
       </c>
-      <c r="F8" s="74">
-        <v>0</v>
-      </c>
-      <c r="G8" s="118">
+      <c r="F8" s="73">
+        <v>0</v>
+      </c>
+      <c r="G8" s="117">
         <f>E8-F8</f>
         <v>0</v>
       </c>
@@ -3108,7 +3072,7 @@
         <v>716400</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>6</v>
       </c>
@@ -3118,16 +3082,16 @@
       <c r="C9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="117">
+      <c r="D9" s="116">
         <v>0.17649999999999999</v>
       </c>
       <c r="E9" s="34">
         <v>0</v>
       </c>
-      <c r="F9" s="74">
-        <v>0</v>
-      </c>
-      <c r="G9" s="118">
+      <c r="F9" s="73">
+        <v>0</v>
+      </c>
+      <c r="G9" s="117">
         <f>E9-F9</f>
         <v>0</v>
       </c>
@@ -3140,13 +3104,13 @@
         <v>794250</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="119" t="s">
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="120"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="122">
+      <c r="B10" s="119"/>
+      <c r="C10" s="120"/>
+      <c r="D10" s="121">
         <f>SUM(D4:D9)</f>
         <v>1</v>
       </c>
@@ -3162,7 +3126,7 @@
         <f>SUM(G4:G9)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="123">
+      <c r="H10" s="122">
         <f t="shared" ref="H10" si="4">SUM(H4:H9)</f>
         <v>4500000</v>
       </c>
@@ -3171,21 +3135,21 @@
         <v>4500000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="127"/>
+      <c r="B11" s="127"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I12" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
     </row>
